--- a/Stats Sheet/Round Gaps/Phobia.xlsx
+++ b/Stats Sheet/Round Gaps/Phobia.xlsx
@@ -634,9 +634,6 @@
     <x:t>Krenzinator</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
-  </x:si>
-  <x:si>
     <x:t>LordLaelaps</x:t>
   </x:si>
   <x:si>
@@ -644,6 +641,9 @@
   </x:si>
   <x:si>
     <x:t>nihontiger</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>pigghetti</x:t>
@@ -4741,30 +4741,9 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="X101" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Y101" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Z101" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="AA101" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="AC101" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="AD101" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="AE101" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="AF101" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
@@ -4813,9 +4792,30 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="D104" s="0">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="X104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Y104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Z104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AA104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AC104" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="AD104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AE104" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="AF104" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
